--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1138,55 +1138,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1243,20 +1243,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Astro Growth Agency</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>propio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1cc4f2e4a6b078</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II, Data Products</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,15 +3041,610 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data &amp; Integrations Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Alternate Solutions Health Network</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nSCALE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nSCALE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Barstow, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Defense Unicorns</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PCA Data Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DPR Construction</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Technology Ventures</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Crescent Energy</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Atmosera</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=e377567986c06890</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e377567986c06890</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Astro Growth Agency</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>propio</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1cc4f2e4a6b078</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,29 +3286,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>API Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9443960b40fa54c3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Engineer II, Data Products</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,41 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e377567986c06890</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>AI Mobile Developer / Co-Founder</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Info Dhas Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Architect New</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=5097124275f0ddf7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Intelerad</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>API Architect (Onsite Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9443960b40fa54c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>API Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=9443960b40fa54c3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>API Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=5d9c6043097083ea</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II, Data Products</t>
+          <t>Corporate Data Engineering Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>MCKIM &amp; CREED</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,15 +3601,225 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kash Tech</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Crescent Energy</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f624140c0ed8f4</t>
+          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Mobile Developer / Co-Founder</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Info Dhas Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,29 +2061,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Info Dhas Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Astro Growth Agency</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect New</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5097124275f0ddf7</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
         </is>
       </c>
     </row>
@@ -2673,52 +2673,52 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Third Sector Intelligence</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
+          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Intelerad</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
@@ -3058,52 +3058,52 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Infrastructure Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,29 +3461,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>API Architect (Onsite Hybrid)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9443960b40fa54c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer (Generative AI / AWS Bedrock)</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, MLOps, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3212b5880946b7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>API Architect (Onsite Hybrid)</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d9c6043097083ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ca76cbde51b6d903</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Corporate Data Engineering Specialist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MCKIM &amp; CREED</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer II, Data Products</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3750,76 +3750,6 @@
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Info Dhas Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Info Dhas Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Astro Growth Agency</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Third Sector Intelligence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Third Sector Intelligence</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Sr Infrastructure Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,69 +3041,69 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Infrastructure Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca76cbde51b6d903</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=ca76cbde51b6d903</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer II, Data Products</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,15 +3741,85 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Korber/Infios Functional/Technical Consultant Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>JGA LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=a32324eea89ff005</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Info Dhas Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,54 +2071,54 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Astro Growth Agency</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Third Sector Intelligence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Third Sector Intelligence</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Sr Infrastructure Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Infrastructure Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
+          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=ca76cbde51b6d903</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca76cbde51b6d903</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Engineer II, Data Products</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3785,41 +3785,6 @@
         </is>
       </c>
       <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Radcube LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc21fd5e8801cab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Korber/Infios Functional/Technical Consultant Remote</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JGA LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32324eea89ff005</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Korber/Infios Functional/Technical Consultant Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JGA LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=a32324eea89ff005</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Astro Growth Agency</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,94 +2596,94 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Third Sector Intelligence</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Third Sector Intelligence</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Sr Infrastructure Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Infrastructure Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
+          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>ThoughtFocus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Hive, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=071b0987d8e950fc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca76cbde51b6d903</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II, Data Products</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3645,146 +3645,6 @@
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Crescent Energy</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Radcube LLC</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warrenton, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc21fd5e8801cab</t>
+          <t>https://www.indeed.com/viewjob?jk=1d393e51b035c281</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb1cf3c611caa16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Radcube LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc21fd5e8801cab</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Korber/Infios Functional/Technical Consultant Remote</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JGA LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32324eea89ff005</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Solutions Engineer - Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Fusion Global Technologies and Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Astro Growth Agency</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9ea26f5dcba01b</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292d723fc85f4776</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Third Sector Intelligence</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,64 +2831,64 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2897,108 +2897,108 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Infrastructure Developer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, Git, Bitbucket, Python, SQL</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff76177b5f1eb624</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Ops Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ThoughtFocus</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Hive, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b0987d8e950fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer II, Data Products</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,260 +3391,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Crescent Energy</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer - Senior</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fusion Global Technologies and Solutions</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,122 +976,122 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Application and Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Solutions Engineer - Senior</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Fusion Global Technologies and Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcc40ac4135e57b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr. Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Kutir Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=9a2954cbf5577991</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,112 +2586,112 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,112 +2831,112 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,102 +2946,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer II, Data Products</t>
+          <t>Data Analyst (Central Analytics)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,330 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Crescent Energy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,172 +671,172 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b1fb1994e004</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b90ba0693590e08c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffbf7a09316e2165</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=08e4dd1f3067be9e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=8609d2ef4d027ec5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,172 +846,172 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=69f6c19dec765945</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a0e6bed4dca46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=4d35c6ea0da8f1a8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=179c827d021e8289</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=b855a0d2171ea7ad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad704e5b438ba778</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Application and Data Architect</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
+          <t>https://www.indeed.com/viewjob?jk=240d4b0b28339cb9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer - Senior</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fusion Global Technologies and Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,137 +1091,137 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c37effbf9d8ae</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>19.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4bf0540050adfb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>19.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0addd50fb05f38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Enterprise Application and Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcc40ac4135e57b</t>
+          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,147 +1546,147 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>IT Solutions Engineer - Senior</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Fusion Global Technologies and Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Columbia SC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=f177ac36447561f1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1698,20 +1698,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1733,20 +1733,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05f96d61fcc07f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcc40ac4135e57b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,207 +2141,207 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kutir Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a2954cbf5577991</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,137 +2456,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Drupal Migration Developer (AWS Focus)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>marvica technologies LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,102 +2946,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,102 +3156,102 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,199 +3261,199 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Sr Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Waterfield Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875609332a8cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst (Central Analytics)</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,29 +3531,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer II, Data Products</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,505 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Services Intern</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ryder System</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Analyst (Central Analytics)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Advisor Solution Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HJ Staffing</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Advisor Solution Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HJ Staffing</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Crescent Energy</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,129 +1336,129 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Spark, Scala, Kafka, Dask, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enterprise Application and Data Architect</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer - Senior</t>
+          <t>Enterprise Application and Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fusion Global Technologies and Solutions</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Columbia SC</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>cooking</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f177ac36447561f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>IT Solutions Engineer - Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>Fusion Global Technologies and Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
@@ -2113,87 +2113,87 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RSVP Communications, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7cbad6a0c86eb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Drupal Migration Developer (AWS Focus)</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>marvica technologies LLC</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>Senior Drupal Migration Developer (AWS Focus)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>marvica technologies LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with AI</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,94 +3156,94 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d31b22f171848fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Waterfield Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e47e0cb8529c9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=a1828374aa7504d0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf7f2fc21997a1c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=3691403890861ce1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,137 +3471,137 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Services Intern</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analyst (Central Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Services Intern</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Analyst (Central Analytics)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer II, Data Products</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,262 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Crescent Energy</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AI or ML Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>React JS and Node JS Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b1fb1994e004</t>
+          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90ba0693590e08c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b1fb1994e004</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffbf7a09316e2165</t>
+          <t>https://www.indeed.com/viewjob?jk=b90ba0693590e08c</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e4dd1f3067be9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffbf7a09316e2165</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8609d2ef4d027ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=08e4dd1f3067be9e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f6c19dec765945</t>
+          <t>https://www.indeed.com/viewjob?jk=8609d2ef4d027ec5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a0e6bed4dca46</t>
+          <t>https://www.indeed.com/viewjob?jk=69f6c19dec765945</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d35c6ea0da8f1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a0e6bed4dca46</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179c827d021e8289</t>
+          <t>https://www.indeed.com/viewjob?jk=4d35c6ea0da8f1a8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b855a0d2171ea7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=179c827d021e8289</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad704e5b438ba778</t>
+          <t>https://www.indeed.com/viewjob?jk=b855a0d2171ea7ad</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=240d4b0b28339cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad704e5b438ba778</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c37effbf9d8ae</t>
+          <t>https://www.indeed.com/viewjob?jk=240d4b0b28339cb9</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4bf0540050adfb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c37effbf9d8ae</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0addd50fb05f38</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4bf0540050adfb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0addd50fb05f38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bain Capital</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Spark, Scala, Kafka, Dask, Snowflake, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,49 +1441,49 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Spark, Scala, Kafka, Dask, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Application and Data Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Enterprise Application and Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer - Senior</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fusion Global Technologies and Solutions</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>IT Solutions Engineer - Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>Fusion Global Technologies and Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcc40ac4135e57b</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RSVP Communications, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,94 +2176,94 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7cbad6a0c86eb</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>RSVP Communications, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7cbad6a0c86eb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,24 +2306,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with AI</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,77 +3111,77 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Cloud Software Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Stratagen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Cloud Storage, Hadoop, Scala, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=22e861ddd0f6e4bb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AWS Technical Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=b74e8628189b9b63</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
+          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1828374aa7504d0</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf7f2fc21997a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691403890861ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,42 +3496,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Waukegan, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, RDS, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=0d933bdd873b035b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=56210093c832adbc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Data Services Intern</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Data Analyst (Central Analytics)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Services Intern</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
+          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Analyst (Central Analytics)</t>
+          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
+          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI or ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,155 +4301,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Crescent Energy</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>AI or ML Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
         </is>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer - Senior</t>
+          <t>Columbia SC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fusion Global Technologies and Solutions</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f177ac36447561f1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>IT Solutions Engineer - Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>Fusion Global Technologies and Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfc97622cac432</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RSVP Communications, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>RSVP Communications, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7cbad6a0c86eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7cbad6a0c86eb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Drupal Migration Developer (AWS Focus)</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>marvica technologies LLC</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Senior Drupal Migration Developer (AWS Focus)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>marvica technologies LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Verona, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
         </is>
       </c>
     </row>
@@ -3128,87 +3128,87 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Software Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Stratagen</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Hadoop, Scala, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e861ddd0f6e4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Technical Architect</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74e8628189b9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Cloud Software Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Stratagen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>Azure, Cloud Storage, Hadoop, Scala, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=22e861ddd0f6e4bb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>AWS Technical Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=b74e8628189b9b63</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Third Sector Intelligence</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
+          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,42 +3496,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,77 +3611,77 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Sr Infrastructure Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Waukegan, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, RDS, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d933bdd873b035b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, Snowflake, MLOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56210093c832adbc</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Services Intern</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analyst (Central Analytics)</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waukegan, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, RDS, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d933bdd873b035b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+          <t>AI Data Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=56210093c832adbc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Services Intern</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Analyst (Central Analytics)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
+          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI or ML Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,157 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-2</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AI or ML Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-08.xlsx
+++ b/results/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b1fb1994e004</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90ba0693590e08c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffbf7a09316e2165</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e4dd1f3067be9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Kinesis, Spark, Scala, Kafka, Dask, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,137 +846,137 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8609d2ef4d027ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f6c19dec765945</t>
+          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a0e6bed4dca46</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d35c6ea0da8f1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179c827d021e8289</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b855a0d2171ea7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,277 +1056,277 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad704e5b438ba778</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=240d4b0b28339cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c37effbf9d8ae</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4bf0540050adfb</t>
+          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0addd50fb05f38</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.8</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
+          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bain Capital</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Spark, Scala, Kafka, Dask, Snowflake, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,137 +1476,137 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>RSVP Communications, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90c850ef759863c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enterprise Application and Data Architect</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0f5e29e8863a92</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Columbia SC</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cooking</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f177ac36447561f1</t>
+          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer - Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fusion Global Technologies and Solutions</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1e89f92944d8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfc97622cac432</t>
+          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,277 +1826,277 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Sr. Data Engineer - Business Delivery</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RSVP Communications, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7cbad6a0c86eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Verona, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b4dfc7167a5b63</t>
+          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Drupal Migration Developer (AWS Focus)</t>
+          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>marvica technologies LLC</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127117f1aa0b751f</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,102 +2911,102 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac81167ddd87b402</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>PCA Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>DPR Construction</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verona, NY, US USA</t>
+          <t>Raleigh-Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfa8ce1c2da6ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3107,186 +3107,186 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9cfb4148755453</t>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Cloud and DevOps Expert</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fresenius Medical Care</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,1162 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Cloud Software Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Stratagen</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Azure, Cloud Storage, Hadoop, Scala, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22e861ddd0f6e4bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>AWS Technical Architect</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b74e8628189b9b63</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>AI Intern</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Ryder System</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Third Sector Intelligence</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior OAS/ODI Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>International Logic Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Fairfax, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Finance BI Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Novo Nordisk, Inc.</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Plainsboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Keck Medicine of USC</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Engineer- Commission and Heap analytics</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf79efb8b86fb13</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Woodbridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr Infrastructure Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Transportation Data Scientist</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Downers Grove, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>TrueML</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>State Farm</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer III</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Cadre5</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Cloud Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>TRC</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0a510d31944601</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Application Support Engineer || Atlanta, GA || Hybrid</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Infoorigin Inc</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b827c56c96c5e274</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>PCA Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>DPR Construction</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Raleigh-Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AWS Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Waukegan, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, RDS, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d933bdd873b035b</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AI Data Architect</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56210093c832adbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Services Intern</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Ryder System</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Data Analyst (Central Analytics)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, CI/CD, Airflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Advisor Solution Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>HJ Staffing</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Advisor Solution Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>HJ Staffing</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1619e772a816828</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Resiliency &amp; Recovery Engineer-2</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=388e699eeed13b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>AI or ML Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Bloomberg</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a74c4f6efd069a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=75e22059c1c4550f</t>
         </is>
       </c>
     </row>
